--- a/proposal/05_Cost_and_Pricing_Model.xlsx
+++ b/proposal/05_Cost_and_Pricing_Model.xlsx
@@ -204,7 +204,7 @@
     <t xml:space="preserve">%</t>
   </si>
   <si>
-    <t xml:space="preserve">GCC corpora often have many scanned Arabic pages</t>
+    <t xml:space="preserve">Assumption pending sight of the corpus; older contracts and board papers are often scanned. Confirm at discovery</t>
   </si>
   <si>
     <t xml:space="preserve">New documents per month (share of corpus)</t>
@@ -360,7 +360,7 @@
     <t xml:space="preserve">USD / 1,000 pages</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure pricing, UAE North; verify current rate</t>
+    <t xml:space="preserve">Azure pricing, Malaysia West / Southeast Asia; verify current rate</t>
   </si>
   <si>
     <t xml:space="preserve">Supabase Pro (pilot database, storage, auth)</t>
@@ -381,19 +381,19 @@
     <t xml:space="preserve">vercel.com/pricing, 2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Managed PostgreSQL in GCC region, tier 1</t>
+    <t xml:space="preserve">Managed PostgreSQL in region, tier 1</t>
   </si>
   <si>
     <t xml:space="preserve">AWS RDS / Azure Database, mid-size instance with storage; estimate</t>
   </si>
   <si>
-    <t xml:space="preserve">Managed PostgreSQL in GCC region, tier 2 (HA)</t>
+    <t xml:space="preserve">Managed PostgreSQL in region, tier 2 (HA)</t>
   </si>
   <si>
     <t xml:space="preserve">Multi-AZ, larger instance, PITR; estimate</t>
   </si>
   <si>
-    <t xml:space="preserve">Managed PostgreSQL in GCC region, tier 3 (HA, read replicas)</t>
+    <t xml:space="preserve">Managed PostgreSQL in region, tier 3 (HA, read replicas)</t>
   </si>
   <si>
     <t xml:space="preserve">Estimate</t>
@@ -423,7 +423,7 @@
     <t xml:space="preserve">USD / hour</t>
   </si>
   <si>
-    <t xml:space="preserve">Hyperscaler GCC region on-demand; reserved pricing 30-50% lower; verify</t>
+    <t xml:space="preserve">Hyperscaler Southeast Asia region on-demand; reserved pricing 30-50% lower; verify</t>
   </si>
   <si>
     <t xml:space="preserve">Hours per month</t>
@@ -525,7 +525,7 @@
     <t xml:space="preserve">UX designer</t>
   </si>
   <si>
-    <t xml:space="preserve">Interface, Arabic layout</t>
+    <t xml:space="preserve">Interface, multilingual layout</t>
   </si>
   <si>
     <t xml:space="preserve">Security and DevOps specialist</t>
@@ -537,7 +537,7 @@
     <t xml:space="preserve">Blended weekly rate used for fees (set this)</t>
   </si>
   <si>
-    <t xml:space="preserve">Indicative market ranges per person-week (2026): South Asia 1,000-2,000; Eastern Europe 2,500-4,500; GCC-based / UK / US 5,000-9,000. Set rates to match your delivery model.</t>
+    <t xml:space="preserve">Indicative market ranges per person-week (2026): South Asia 1,000-2,000; Southeast Asia 1,500-3,000; Eastern Europe 2,500-4,500; GCC / UK / US 5,000-9,000. Set rates to match your delivery model.</t>
   </si>
   <si>
     <t xml:space="preserve">Managed service: support tier as share of annual platform fee</t>
@@ -1718,7 +1718,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
         <v>34</v>
       </c>
